--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,136 +923,136 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
+        <v>300</v>
+      </c>
+      <c r="M15" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="N15" s="15">
         <v>100</v>
-      </c>
-      <c r="M15" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="N15" s="15">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.487179487179</v>
+        <v>-82.608695652173</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
+        <v>12</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-41.666666666666</v>
+      </c>
+      <c r="I17" s="14">
         <v>14</v>
       </c>
-      <c r="H17" s="15">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="I17" s="14">
-        <v>10</v>
-      </c>
       <c r="J17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K17" s="15">
-        <v>-47.368421052631</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-41.176470588235</v>
+        <v>-30</v>
       </c>
       <c r="M17" s="15">
-        <v>-37.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.538461538461</v>
+        <v>-51.724137931034</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="14">
         <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-70</v>
+        <v>-76</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.862068965517</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>28.571428571428</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>32</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J19" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K19" s="15">
-        <v>23.684210526315</v>
+        <v>34.090909090909</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.616438356164</v>
+        <v>-28.915662650602</v>
       </c>
       <c r="M19" s="15">
-        <v>4.444444444444</v>
+        <v>15.686274509803</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.462365591397</v>
+        <v>-45.370370370370</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,20 +1103,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
@@ -1131,10 +1131,10 @@
         <v>20</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.107255520504</v>
+        <v>-98.324022346368</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
         <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>8.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.344827586206</v>
+        <v>1.694915254237</v>
       </c>
       <c r="I21" s="17">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J21" s="17">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.058823529411</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.522935779816</v>
+        <v>-22.4</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.549019607843</v>
+        <v>-19.834710743801</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.898839137645</v>
+        <v>-85.901162790697</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-54.166666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15">
-        <v>-41.25</v>
+        <v>-31.506849315068</v>
       </c>
       <c r="I24" s="14">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="J24" s="14">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K24" s="15">
-        <v>-42.622950819672</v>
+        <v>-36.764705882352</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.038834951456</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="M24" s="15">
-        <v>-59.302325581395</v>
+        <v>-56.345177664974</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.857142857142</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-61.403508771929</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="I25" s="14">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K25" s="15">
-        <v>-63.157894736842</v>
+        <v>-54.216867469879</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.695652173913</v>
+        <v>30</v>
       </c>
       <c r="I26" s="14">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J26" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K26" s="15">
-        <v>-32.432432432432</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.846153846153</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M26" s="15">
-        <v>-44.444444444444</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
         <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
         <v>33.333333333333</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14">
         <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.272727272727</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.608695652173</v>
+        <v>-80.392156862745</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,79 +980,79 @@
       <c r="C17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
-      <c r="E17" s="15">
-        <v>50</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
+        <v>8</v>
+      </c>
+      <c r="G17" s="14">
         <v>7</v>
       </c>
-      <c r="G17" s="14">
-        <v>12</v>
-      </c>
       <c r="H17" s="15">
-        <v>-41.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J17" s="14">
         <v>21</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.333333333333</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L17" s="15">
-        <v>-30</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M17" s="15">
-        <v>-36.363636363636</v>
+        <v>-32</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.724137931034</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-64.285714285714</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-71.428571428571</v>
+        <v>-72</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="M18" s="15">
-        <v>-76</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.862068965517</v>
+        <v>-96.111111111111</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>83.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
         <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>46.153846153846</v>
+        <v>22.580645161290</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J19" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K19" s="15">
-        <v>34.090909090909</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.915662650602</v>
+        <v>-31.25</v>
       </c>
       <c r="M19" s="15">
-        <v>15.686274509803</v>
+        <v>17.857142857142</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.370370370370</v>
+        <v>-45.901639344262</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.324022346368</v>
+        <v>-98.557692307692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F21" s="17">
         <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H21" s="18">
-        <v>1.694915254237</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="J21" s="17">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>-1.785714285714</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.4</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.834710743801</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.901162790697</v>
+        <v>-86.335403726708</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,11 +1226,11 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1242,19 +1242,19 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>14.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G24" s="14">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.506849315068</v>
+        <v>-38.823529411764</v>
       </c>
       <c r="I24" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J24" s="14">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="K24" s="15">
-        <v>-36.764705882352</v>
+        <v>-40.853658536585</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.746031746031</v>
+        <v>-32.167832167832</v>
       </c>
       <c r="M24" s="15">
-        <v>-56.345177664974</v>
+        <v>-57.079646017699</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>42.857142857142</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.938775510204</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="K25" s="15">
-        <v>-54.216867469879</v>
+        <v>-56.701030927835</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.142857142857</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
         <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H26" s="15">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="I26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J26" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.195121951219</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="L26" s="15">
-        <v>5.882352941176</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="M26" s="15">
-        <v>-32.075471698113</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1432,28 +1432,28 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L28" s="15">
         <v>33.333333333333</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -926,10 +926,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
         <v>33.333333333333</v>
-      </c>
-      <c r="N15" s="15">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,7 +937,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -949,28 +949,28 @@
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
         <v>6</v>
       </c>
       <c r="K16" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.076923076923</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.392156862745</v>
+        <v>-81.034482758620</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,79 +980,79 @@
       <c r="C17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="14">
+        <v>9</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>14.285714285714</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J17" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>-19.047619047619</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-34.615384615384</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>-32</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-52.380952380952</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-53.846153846153</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-72</v>
+        <v>-73.076923076923</v>
       </c>
       <c r="L18" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.074074074074</v>
+        <v>-78.125</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.111111111111</v>
+        <v>-96.744186046511</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>22.580645161290</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K19" s="15">
-        <v>22.222222222222</v>
+        <v>22.413793103448</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.25</v>
+        <v>-29.702970297029</v>
       </c>
       <c r="M19" s="15">
-        <v>17.857142857142</v>
+        <v>7.575757575757</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.901639344262</v>
+        <v>-48.920863309352</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
@@ -1119,22 +1119,22 @@
         <v>-75</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.557692307692</v>
+        <v>-98.488120950324</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
         <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.785714285714</v>
+        <v>-5.511811023622</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.666666666666</v>
+        <v>-27.710843373494</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.910447761194</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.335403726708</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,32 +1223,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-57.142857142857</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="F24" s="14">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.823529411764</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="I24" s="14">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J24" s="14">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>-40.853658536585</v>
+        <v>-45.405405405405</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.167832167832</v>
+        <v>-38.036809815950</v>
       </c>
       <c r="M24" s="15">
-        <v>-57.079646017699</v>
+        <v>-59.6</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.058823529411</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K25" s="15">
-        <v>-56.701030927835</v>
+        <v>-58.878504672897</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.384615384615</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
         <v>10</v>
       </c>
       <c r="H26" s="15">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="I26" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.976744186046</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.439024390243</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="M26" s="15">
-        <v>-35.483870967741</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,20 +1431,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -936,32 +936,32 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L16" s="15">
         <v>-15.384615384615</v>
@@ -970,7 +970,7 @@
         <v>-15.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.034482758620</v>
+        <v>-83.582089552238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
         <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.076923076923</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="L17" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M17" s="15">
-        <v>-23.076923076923</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.380952380952</v>
+        <v>-55.319148936170</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
+        <v>10</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-70</v>
+      </c>
+      <c r="I18" s="14">
         <v>9</v>
       </c>
-      <c r="H18" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I18" s="14">
-        <v>7</v>
-      </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-73.076923076923</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.125</v>
+        <v>-73.529411764705</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.744186046511</v>
+        <v>-96.341463414634</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
         <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>22.222222222222</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J19" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>22.413793103448</v>
+        <v>20</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.702970297029</v>
+        <v>-28.440366972477</v>
       </c>
       <c r="M19" s="15">
-        <v>7.575757575757</v>
+        <v>9.859154929577</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.920863309352</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
-      </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-75</v>
-      </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
         <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.488120950324</v>
+        <v>-98.455598455598</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.511811023622</v>
+        <v>-7.092198581560</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.710843373494</v>
+        <v>-28.415300546448</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.568627450980</v>
+        <v>-21.556886227544</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.956521739130</v>
+        <v>-87.367405978785</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1236,22 +1236,22 @@
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>21</v>
+        <v>-20</v>
+      </c>
+      <c r="L23" s="15">
+        <v>300</v>
       </c>
       <c r="M23" s="15">
         <v>33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-80.952380952380</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>-51.724137931034</v>
+        <v>-43.421052631578</v>
       </c>
       <c r="I24" s="14">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="K24" s="15">
-        <v>-45.405405405405</v>
+        <v>-42.929292929292</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.036809815950</v>
+        <v>-38.918918918918</v>
       </c>
       <c r="M24" s="15">
-        <v>-59.6</v>
+        <v>-60.211267605633</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.666666666666</v>
+        <v>-48.717948717948</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.878504672897</v>
+        <v>-58.260869565217</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.589743589743</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>140</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J26" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.347826086956</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.725490196078</v>
+        <v>-20.338983050847</v>
       </c>
       <c r="M26" s="15">
-        <v>-35.294117647058</v>
+        <v>-39.743589743589</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-55.555555555555</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1613,29 +1613,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>2</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -923,13 +923,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
+        <v>-20</v>
+      </c>
+      <c r="M15" s="15">
+        <v>-20</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
-        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -958,19 +958,19 @@
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="L16" s="15">
         <v>-15.384615384615</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.582089552238</v>
+        <v>-84.285714285714</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>-30</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="I17" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>-38.235294117647</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L17" s="15">
-        <v>-36.363636363636</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="M17" s="15">
-        <v>-36.363636363636</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.319148936170</v>
+        <v>-47.169811320754</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,13 +1019,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -1037,22 +1037,22 @@
         <v>-70</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-67.857142857142</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.714285714285</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.529411764705</v>
+        <v>-70.270270270270</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.341463414634</v>
+        <v>-95.925925925925</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
         <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>20</v>
+        <v>28.169014084507</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.440366972477</v>
+        <v>-26.016260162601</v>
       </c>
       <c r="M19" s="15">
-        <v>9.859154929577</v>
+        <v>19.736842105263</v>
       </c>
       <c r="N19" s="15">
-        <v>-50</v>
+        <v>-45.508982035928</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
         <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.455598455598</v>
+        <v>-98.432055749128</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.714285714285</v>
+        <v>-14.0625</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.092198581560</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.415300546448</v>
+        <v>-25.603864734299</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.556886227544</v>
+        <v>-14.444444444444</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.367405978785</v>
+        <v>-86.467486818980</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1227,28 +1227,28 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L23" s="15">
         <v>300</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.285714285714</v>
+        <v>6.25</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>-43.421052631578</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I24" s="14">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="J24" s="14">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="K24" s="15">
-        <v>-42.929292929292</v>
+        <v>-39.252336448598</v>
       </c>
       <c r="L24" s="15">
-        <v>-38.918918918918</v>
+        <v>-37.198067632850</v>
       </c>
       <c r="M24" s="15">
-        <v>-60.211267605633</v>
+        <v>-58.199356913183</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-48.717948717948</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J25" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.260869565217</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.454545454545</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-62.5</v>
+        <v>120</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>35.294117647058</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J26" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.962962962963</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.338983050847</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.743589743589</v>
+        <v>-34.831460674157</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>3</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,17 +1554,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1573,7 +1573,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>
@@ -1613,11 +1613,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -940,37 +940,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K16" s="15">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.285714285714</v>
+        <v>-85.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-39.130434782608</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>-36.363636363636</v>
+        <v>-34.693877551020</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.707317073170</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="M17" s="15">
-        <v>-22.222222222222</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.169811320754</v>
+        <v>-44.827586206896</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-70</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-64.516129032258</v>
+        <v>-62.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.666666666666</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.270270270270</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.925925925925</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>116.666666666667</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>18.518518518518</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K19" s="15">
-        <v>28.169014084507</v>
+        <v>17.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.016260162601</v>
+        <v>-28.787878787878</v>
       </c>
       <c r="M19" s="15">
-        <v>19.736842105263</v>
+        <v>14.634146341463</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.508982035928</v>
+        <v>-49.462365591397</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1122,19 +1122,19 @@
         <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="15">
         <v>-10</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.432055749128</v>
+        <v>-98.566878980891</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>10</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.0625</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="I21" s="17">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J21" s="17">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.347826086956</v>
+        <v>-9.497206703910</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.603864734299</v>
+        <v>-27.678571428571</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.444444444444</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.467486818980</v>
+        <v>-86.924939467312</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>300</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>6.25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-42.307692307692</v>
+        <v>-30.882352941176</v>
       </c>
       <c r="I24" s="14">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J24" s="14">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="K24" s="15">
-        <v>-39.252336448598</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.198067632850</v>
+        <v>-37.117903930131</v>
       </c>
       <c r="M24" s="15">
-        <v>-58.199356913183</v>
+        <v>-57.771260997067</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>44.444444444444</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="14">
         <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.902439024390</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I25" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.612903225806</v>
+        <v>-51.145038167938</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.393939393939</v>
+        <v>-42.342342342342</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
         <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>120</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>22.222222222222</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.694915254237</v>
+        <v>-4.6875</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.121212121212</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="M26" s="15">
-        <v>-34.831460674157</v>
+        <v>-39.603960396039</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1432,31 +1432,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1578,8 +1578,8 @@
       <c r="K31" s="15">
         <v>-100</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I16" s="14">
+        <v>12</v>
+      </c>
+      <c r="J16" s="14">
         <v>11</v>
       </c>
-      <c r="J16" s="14">
-        <v>10</v>
-      </c>
       <c r="K16" s="15">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.666666666666</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.333333333333</v>
+        <v>-84.810126582278</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>-46.428571428571</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.693877551020</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.581395348837</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="M17" s="15">
-        <v>-17.948717948717</v>
+        <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.827586206896</v>
+        <v>-37.096774193548</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
         <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-62.5</v>
+        <v>-43.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.842105263157</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.230769230769</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.833333333333</v>
+        <v>-94.321766561514</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>7.692307692307</v>
+        <v>6.060606060606</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J19" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>17.5</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.787878787878</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M19" s="15">
-        <v>14.634146341463</v>
+        <v>17.977528089887</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.462365591397</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.566878980891</v>
+        <v>-98.372781065088</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-55.555555555555</v>
+        <v>56.25</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.880597014925</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.497206703910</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.678571428571</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.923076923076</v>
+        <v>-9.134615384615</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.924939467312</v>
+        <v>-85.874439461883</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-85.714285714285</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L23" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.882352941176</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="I24" s="14">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="J24" s="14">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.931034482758</v>
+        <v>-35.458167330677</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.117903930131</v>
+        <v>-36.220472440944</v>
       </c>
       <c r="M24" s="15">
-        <v>-57.771260997067</v>
+        <v>-55</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.352941176470</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.145038167938</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.342342342342</v>
+        <v>-39.0625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
         <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.761904761904</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.6875</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.294117647058</v>
+        <v>-12.162162162162</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.603960396039</v>
+        <v>-39.252336448598</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1456,7 +1456,7 @@
         <v>-38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,8 +1543,8 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>-20</v>
@@ -946,31 +946,31 @@
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
+        <v>13</v>
+      </c>
+      <c r="J16" s="14">
         <v>12</v>
       </c>
-      <c r="J16" s="14">
-        <v>11</v>
-      </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.842105263157</v>
+        <v>-35</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-35</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.810126582278</v>
+        <v>-84.146341463414</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.739130434782</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I17" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K17" s="15">
-        <v>-26.415094339622</v>
+        <v>-20</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.363636363636</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>4.761904761904</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.096774193548</v>
+        <v>-34.328358208955</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.75</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.142857142857</v>
+        <v>-59.574468085106</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.321766561514</v>
+        <v>-94.540229885057</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>6.060606060606</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="I19" s="14">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>15.384615384615</v>
+        <v>8.080808080808</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.571428571428</v>
+        <v>-31.410256410256</v>
       </c>
       <c r="M19" s="15">
-        <v>17.977528089887</v>
+        <v>7</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.5</v>
+        <v>-50.691244239631</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>300</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="L20" s="15">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.372781065088</v>
+        <v>-97.802197802197</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
         <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>56.25</v>
+        <v>-6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
         <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="J21" s="17">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.076923076923</v>
+        <v>-3.791469194312</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.857142857142</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.134615384615</v>
+        <v>-11.353711790393</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.874439461883</v>
+        <v>-85.961272475795</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,23 +1223,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.263157894736</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.462686567164</v>
+        <v>-9.589041095890</v>
       </c>
       <c r="I24" s="14">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J24" s="14">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.458167330677</v>
+        <v>-34.317343173431</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.220472440944</v>
+        <v>-33.828996282527</v>
       </c>
       <c r="M24" s="15">
-        <v>-55</v>
+        <v>-53.886010362694</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>12.903225806451</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J25" s="14">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.478260869565</v>
+        <v>-45.033112582781</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.0625</v>
+        <v>-38.518518518518</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
+        <v>50</v>
+      </c>
+      <c r="F26" s="14">
+        <v>24</v>
+      </c>
+      <c r="G26" s="14">
+        <v>17</v>
+      </c>
+      <c r="H26" s="15">
+        <v>41.176470588235</v>
+      </c>
+      <c r="I26" s="14">
+        <v>71</v>
+      </c>
+      <c r="J26" s="14">
+        <v>71</v>
+      </c>
+      <c r="K26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>21</v>
-      </c>
-      <c r="G26" s="14">
-        <v>21</v>
-      </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
-      <c r="I26" s="14">
-        <v>65</v>
-      </c>
-      <c r="J26" s="14">
-        <v>67</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-2.985074626865</v>
-      </c>
       <c r="L26" s="15">
-        <v>-12.162162162162</v>
+        <v>-12.345679012345</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.252336448598</v>
+        <v>-37.168141592920</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1447,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-38.461538461538</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -940,37 +940,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I16" s="14">
+        <v>14</v>
+      </c>
+      <c r="J16" s="14">
+        <v>14</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>2</v>
-      </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-60</v>
-      </c>
-      <c r="I16" s="14">
-        <v>13</v>
-      </c>
-      <c r="J16" s="14">
-        <v>12</v>
-      </c>
-      <c r="K16" s="15">
-        <v>8.333333333333</v>
-      </c>
       <c r="L16" s="15">
-        <v>-35</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-35</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.146341463414</v>
+        <v>-84.090909090909</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>4.761904761904</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>-20</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.382978723404</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M17" s="15">
-        <v>4.761904761904</v>
+        <v>11.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.328358208955</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>28.571428571428</v>
+        <v>60</v>
       </c>
       <c r="I18" s="14">
         <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.714285714285</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="L18" s="15">
         <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.574468085106</v>
+        <v>-61.224489795918</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.540229885057</v>
+        <v>-94.892473118279</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
         <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.705882352941</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I19" s="14">
+        <v>112</v>
+      </c>
+      <c r="J19" s="14">
         <v>107</v>
       </c>
-      <c r="J19" s="14">
-        <v>99</v>
-      </c>
       <c r="K19" s="15">
-        <v>8.080808080808</v>
+        <v>4.672897196261</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.410256410256</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="M19" s="15">
-        <v>7</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.691244239631</v>
+        <v>-53.138075313807</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>166.666666666667</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>60</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>60</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>6.666666666666</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.802197802197</v>
+        <v>-97.845373891001</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I21" s="17">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="J21" s="17">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.791469194312</v>
+        <v>-6.113537117903</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.222222222222</v>
+        <v>-22.101449275362</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.353711790393</v>
+        <v>-13.654618473895</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.961272475795</v>
+        <v>-86.297004461440</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,29 +1226,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>-36.363636363636</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L23" s="15">
         <v>133.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.589041095890</v>
+        <v>-25.301204819277</v>
       </c>
       <c r="I24" s="14">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="J24" s="14">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="K24" s="15">
-        <v>-34.317343173431</v>
+        <v>-35.690235690235</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.828996282527</v>
+        <v>-33.216783216783</v>
       </c>
       <c r="M24" s="15">
-        <v>-53.886010362694</v>
+        <v>-54.846335697399</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-61.538461538461</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J25" s="14">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K25" s="15">
-        <v>-45.033112582781</v>
+        <v>-44.848484848484</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.518518518518</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14">
         <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>41.176470588235</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K26" s="15">
         <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.345679012345</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M26" s="15">
-        <v>-37.168141592920</v>
+        <v>-41.085271317829</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,13 +923,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.666666666666</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.090909090909</v>
+        <v>-81.521739130434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>72.727272727272</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J17" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.949152542372</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.921568627450</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>11.363636363636</v>
+        <v>12.765957446808</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.365853658536</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.222222222222</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.636363636363</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.224489795918</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.892473118279</v>
+        <v>-94.683544303797</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-41.666666666666</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="I19" s="14">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J19" s="14">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K19" s="15">
-        <v>4.672897196261</v>
+        <v>2.542372881355</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.707317073170</v>
+        <v>-28.823529411764</v>
       </c>
       <c r="M19" s="15">
-        <v>3.703703703703</v>
+        <v>6.140350877192</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.138075313807</v>
+        <v>-51.984126984127</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,37 +1104,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>30.769230769230</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>41.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-10.526315789473</v>
+        <v>-10</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.845373891001</v>
+        <v>-97.867298578199</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.764705882352</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I21" s="17">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.113537117903</v>
+        <v>-3.673469387755</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.101449275362</v>
+        <v>-18.620689655172</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.654618473895</v>
+        <v>-11.278195488721</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.297004461440</v>
+        <v>-85.859796285200</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-46.153846153846</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L23" s="15">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="M23" s="15">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.301204819277</v>
+        <v>-29.213483146067</v>
       </c>
       <c r="I24" s="14">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="J24" s="14">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.690235690235</v>
+        <v>-35.514018691588</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.216783216783</v>
+        <v>-31.907894736842</v>
       </c>
       <c r="M24" s="15">
-        <v>-54.846335697399</v>
+        <v>-55</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.857142857142</v>
+        <v>-90</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H25" s="15">
-        <v>-24.390243902439</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J25" s="14">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K25" s="15">
-        <v>-44.848484848484</v>
+        <v>-47.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.363636363636</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J26" s="14">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.627906976744</v>
+        <v>-11.458333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-41.085271317829</v>
+        <v>-38.848920863309</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1441,22 +1441,22 @@
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1579,7 +1579,7 @@
         <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>50</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>13.333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.047619047619</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M16" s="15">
         <v>-41.379310344827</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.521739130434</v>
+        <v>-81.720430107526</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>72.727272727272</v>
+        <v>-28</v>
       </c>
       <c r="I17" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.666666666666</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>1.785714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>12.765957446808</v>
+        <v>16.326530612244</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.365853658536</v>
+        <v>-38.043478260869</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>80</v>
+        <v>-37.5</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.243243243243</v>
+        <v>-42.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.5</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.823529411764</v>
+        <v>-56.603773584905</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.683544303797</v>
+        <v>-94.497607655502</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,63 +1060,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.947368421052</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I19" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K19" s="15">
-        <v>2.542372881355</v>
+        <v>2.4</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.823529411764</v>
+        <v>-28.491620111731</v>
       </c>
       <c r="M19" s="15">
-        <v>6.140350877192</v>
+        <v>4.918032786885</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.984126984127</v>
+        <v>-53.284671532846</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
         <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>18</v>
@@ -1128,13 +1128,13 @@
         <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>12.5</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M20" s="15">
-        <v>-10</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.867298578199</v>
+        <v>-97.984322508398</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>9.090909090909</v>
+        <v>-22.784810126582</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="J21" s="17">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.673469387755</v>
+        <v>-9.124087591240</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.620689655172</v>
+        <v>-18.627450980392</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.278195488721</v>
+        <v>-11.071428571428</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.859796285200</v>
+        <v>-85.963923337091</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>7</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="I23" s="14">
         <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15">
-        <v>-35.714285714285</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L23" s="15">
+        <v>50</v>
+      </c>
+      <c r="M23" s="15">
         <v>125</v>
-      </c>
-      <c r="M23" s="15">
-        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F24" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
         <v>89</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.213483146067</v>
+        <v>-26.966292134831</v>
       </c>
       <c r="I24" s="14">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.514018691588</v>
+        <v>-32.647058823529</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.907894736842</v>
+        <v>-30.395136778115</v>
       </c>
       <c r="M24" s="15">
-        <v>-55</v>
+        <v>-53.923541247484</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-90</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.363636363636</v>
+        <v>-43.75</v>
       </c>
       <c r="I25" s="14">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J25" s="14">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.428571428571</v>
+        <v>-43.548387096774</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.025641025641</v>
+        <v>-37.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
         <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.181818181818</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="I26" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.298850574712</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.458333333333</v>
+        <v>-8.910891089108</v>
       </c>
       <c r="M26" s="15">
-        <v>-38.848920863309</v>
+        <v>-40.645161290322</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L28" s="15">
         <v>40</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1487,8 +1487,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1503,15 +1503,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1528,8 +1528,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1544,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -939,17 +939,17 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
         <v>0</v>
@@ -967,10 +967,10 @@
         <v>-22.727272727272</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.379310344827</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.720430107526</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,63 +978,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-77.777777777777</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-28</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>-26.923076923076</v>
+        <v>-30.120481927710</v>
       </c>
       <c r="L17" s="15">
-        <v>1.785714285714</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="M17" s="15">
-        <v>16.326530612244</v>
+        <v>13.725490196078</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.043478260869</v>
+        <v>-39.583333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14">
         <v>5</v>
       </c>
-      <c r="G18" s="14">
-        <v>8</v>
-      </c>
       <c r="H18" s="15">
-        <v>-37.5</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
         <v>23</v>
@@ -1049,10 +1049,10 @@
         <v>-11.538461538461</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.603773584905</v>
+        <v>-57.407407407407</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.497607655502</v>
+        <v>-94.866071428571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.411764705882</v>
+        <v>6.25</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K19" s="15">
-        <v>2.4</v>
+        <v>7.633587786259</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.491620111731</v>
+        <v>-25</v>
       </c>
       <c r="M19" s="15">
-        <v>4.918032786885</v>
+        <v>7.633587786259</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.284671532846</v>
+        <v>-50.871080139372</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
         <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L20" s="15">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.984322508398</v>
+        <v>-98.093220338983</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17">
         <v>13</v>
       </c>
-      <c r="D21" s="17">
-        <v>29</v>
-      </c>
       <c r="E21" s="18">
-        <v>-55.172413793103</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.784810126582</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I21" s="17">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.124087591240</v>
+        <v>-8.362369337979</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.627450980392</v>
+        <v>-17.554858934169</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.071428571428</v>
+        <v>-12.040133779264</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.963923337091</v>
+        <v>-86.025504782146</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
@@ -1236,19 +1236,19 @@
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-80</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="I23" s="14">
         <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L23" s="15">
         <v>50</v>
@@ -1268,34 +1268,34 @@
         <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>5.263157894736</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.966292134831</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="I24" s="14">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="J24" s="14">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.647058823529</v>
+        <v>-30.532212885154</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.395136778115</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="M24" s="15">
-        <v>-53.923541247484</v>
+        <v>-54.327808471454</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>9.090909090909</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
         <v>48</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.75</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J25" s="14">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.548387096774</v>
+        <v>-44.221105527638</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.5</v>
+        <v>-37.640449438202</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
         <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.903225806451</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J26" s="14">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.122448979591</v>
+        <v>-6.422018348623</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.910891089108</v>
+        <v>-4.672897196261</v>
       </c>
       <c r="M26" s="15">
-        <v>-40.645161290322</v>
+        <v>-40.697674418604</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>5</v>
-      </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.315789473684</v>
+        <v>-30</v>
       </c>
       <c r="L28" s="15">
-        <v>40</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1487,8 +1487,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="14">
-        <v>2</v>
+      <c r="I29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1503,15 +1503,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1528,8 +1528,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="14">
-        <v>1</v>
+      <c r="I30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1544,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-122pct.xlsx
+++ b/data/source/weekly/cs-en-us-122pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -898,29 +898,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="14">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15">
+        <v>500</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -929,15 +929,15 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,31 +946,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
         <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>6.25</v>
+        <v>25</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.727272727272</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.484848484848</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.333333333333</v>
+        <v>-81.132075471698</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="F17" s="14">
+        <v>11</v>
+      </c>
+      <c r="G17" s="14">
+        <v>33</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I17" s="14">
+        <v>60</v>
+      </c>
+      <c r="J17" s="14">
+        <v>92</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-34.782608695652</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-1.639344262295</v>
+      </c>
+      <c r="M17" s="15">
+        <v>15.384615384615</v>
+      </c>
+      <c r="N17" s="15">
         <v>-40</v>
-      </c>
-      <c r="F17" s="14">
-        <v>14</v>
-      </c>
-      <c r="G17" s="14">
-        <v>28</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I17" s="14">
-        <v>58</v>
-      </c>
-      <c r="J17" s="14">
-        <v>83</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-30.120481927710</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-1.694915254237</v>
-      </c>
-      <c r="M17" s="15">
-        <v>13.725490196078</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-39.583333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.5</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.538461538461</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.407407407407</v>
+        <v>-56.363636363636</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.866071428571</v>
+        <v>-95.010395010395</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>6.25</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="J19" s="14">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K19" s="15">
-        <v>7.633587786259</v>
+        <v>10.218978102189</v>
       </c>
       <c r="L19" s="15">
-        <v>-25</v>
+        <v>-24.5</v>
       </c>
       <c r="M19" s="15">
-        <v>7.633587786259</v>
+        <v>8.633093525179</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.871080139372</v>
+        <v>-49.833887043189</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,37 +1104,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
+        <v>19</v>
+      </c>
+      <c r="J20" s="14">
         <v>18</v>
       </c>
-      <c r="J20" s="14">
-        <v>17</v>
-      </c>
       <c r="K20" s="15">
-        <v>5.882352941176</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.093220338983</v>
+        <v>-98.078867542972</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
         <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.052631578947</v>
+        <v>-14.473684210526</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="J21" s="17">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.362369337979</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.554858934169</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.040133779264</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.025504782146</v>
+        <v>-85.901309164149</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-84.615384615384</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>-62.5</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>17.647058823529</v>
+        <v>137.5</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.604651162790</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I24" s="14">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="J24" s="14">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.532212885154</v>
+        <v>-26.849315068493</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.545454545454</v>
+        <v>-28.8</v>
       </c>
       <c r="M24" s="15">
-        <v>-54.327808471454</v>
+        <v>-53.965517241379</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-46.153846153846</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.666666666666</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="I25" s="14">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K25" s="15">
-        <v>-44.221105527638</v>
+        <v>-42.079207920792</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.640449438202</v>
+        <v>-36.756756756756</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.421052631578</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="I26" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.422018348623</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.672897196261</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="M26" s="15">
-        <v>-40.697674418604</v>
+        <v>-42.487046632124</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+      <c r="J27" s="14">
+        <v>1</v>
+      </c>
+      <c r="K27" s="15">
+        <v>600</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-30</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>27.272727272727</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
